--- a/docs/test-cases/SPM-26_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-26_Test_Cases.xlsx
@@ -7,14 +7,13 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Questions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC01" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC02" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC03" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC04" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC05" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC06" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC07" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC01" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC02" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC03" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC04" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC05" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC06" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TC07" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -454,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -917,13 +916,39 @@
       </c>
       <c r="F17" s="9" t="n"/>
     </row>
+    <row r="19" ht="98.5" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Code reviewed</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>src/app/api/events/[id]/route.ts
+src/lib/permissions.ts
+src/lib/clarification.ts
+src/app/events/[id]/edit/page.tsx
+src/app/events/[id]/page.tsx
+src/app/events/[id]/ClarificationDetails.tsx
+scripts/seed-spm26.ts</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="8" t="n"/>
+      <c r="G19" s="8" t="n"/>
+      <c r="H19" s="8" t="n"/>
+      <c r="I19" s="9" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B19:I19"/>
     <mergeCell ref="E13:F13"/>
     <mergeCell ref="E14:F14"/>
     <mergeCell ref="B15:D15"/>
@@ -947,102 +972,184 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="75" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="24.77734375" customWidth="1" min="1" max="1"/>
+    <col width="56.77734375" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B1" s="7" t="inlineStr">
-        <is>
-          <t>Question / ambiguity for the PO or developer</t>
-        </is>
-      </c>
-      <c r="C1" s="7" t="inlineStr">
-        <is>
-          <t>Answer</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="71.5" customHeight="1">
-      <c r="A2" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>DECIDED 2026-10-21: Written before the code (test-first). The wording below is decided here and matches the CONTRACT comments in the unit tests (src/lib/__tests__/permissions.test.ts, src/app/api/__tests__/event-detail.test.ts, src/app/__tests__/event-form-pages.test.tsx, src/app/__tests__/event-pages.test.tsx).</t>
-        </is>
-      </c>
-      <c r="C2" s="11" t="n"/>
-    </row>
-    <row r="3" ht="71.5" customHeight="1">
-      <c r="A3" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>DECIDED 2026-10-21: One action. The organiser's edit and the resubmit are a single 'Resubmit request' button on the 'Update request' page (the draft editor at /events/&lt;reference&gt;/edit, opened in response mode). It saves the changes and marks the clarification answered together; there is no 'Save draft' while Under review.</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="n"/>
-    </row>
-    <row r="4" ht="112" customHeight="1">
-      <c r="A4" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>DECIDED 2026-10-21: Wording - 'Update request' button in the event page's 'Clarification requested' banner; page title 'Update request'; button 'Resubmit request' (busy: 'Resubmitting…') and 'Cancel'; after resubmitting, the event page says 'Your updated request has been sent to &lt;coordinator&gt;. It stays Under review.'; refusals 'Could not open this request' with 'Only the organiser who raised this request can update it.' or 'This request has no open clarification to answer, so it can't be changed here.'</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="n"/>
-    </row>
-    <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>DECIDED 2026-10-21: No reply message. The ACs ask for the update and the resubmit only, so responding stores no message (ClarificationRequest.responseMessage stays empty); the clarification is marked answered with the time.</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="n"/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="17.5" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>SPM-26-TC01</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="44.5" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>The organiser who raised the request sees the open clarification on the event and on the Update request page, with the request's current details filled in</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="125.5" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Pre-conditions</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Test data loaded: `npm run fixtures:spm26` has been run from the project folder (it only touches the 'SPM26 …' events, never anyone else's data).
+'SPM26 Meridian Advisory Briefing' is Under review, raised by Rachel Ng and assigned to Daniel Tan, with a clarification Daniel Tan opened on 20 Oct 2026, 10:00 about Description and Expected attendance.
+Logged in as Event Organiser Rachel Ng (rachel.ng@meridianfina.com / password123).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="71.5" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>1. Click 'My Events' in the sidebar and open 'SPM26 Meridian Advisory Briefing'
+2. Click 'Update request' in the 'Clarification requested' banner
+3. Click 'Cancel'</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>DECIDED 2026-10-21: Only the organiser who raised the request can respond - the same rule as editing a draft (SPM-24). Colleagues in the same client still see the clarification (SPM-29 AC3) but get no 'Update request' button (TC06).</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="n"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>DECIDED 2026-10-21: The fields that can be changed are exactly the draft's (SPM-24, AC2), and a resubmitted request must be as complete as a submitted one (the same required fields as 'Submit request'), so a required field cannot be cleared (TC04).</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="n"/>
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Event: SPM26 Meridian Advisory Briefing
+Clarification: Description, Expected attendance - 'How many advisers will attend, and is there a networking session after the briefing?'</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="247" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Step 1: The event page shows the 'Under review' badge and an amber 'Clarification requested' banner listing 'Needs clarification: Description, Expected attendance', the message 'How many advisers will attend, and is there a networking session after the briefing?', 'Asked by Daniel Tan on 20 Oct 2026, 10:00' and an 'Update request' button.
+Step 2: The 'Update request' page opens with the 'Under review' badge. At the top a 'Clarification requested' box shows the same items, message and 'Asked by Daniel Tan on 20 Oct 2026, 10:00'. The form is filled in with the request as it stands: Event name 'SPM26 Meridian Advisory Briefing', Type of event 'Conference', Description 'Half-day session followed by networking.', Expected attendance '80', Preferred room layout 'Theatre'. At the bottom are 'Resubmit request' and 'Cancel'; there is no 'Save draft' or 'Submit request' button.
+Step 3: The event page opens again, still 'Under review', with the same 'Clarification requested' banner and Expected attendance '80'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="17.5" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>Sammi Chua</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Creation Date</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="n">
+        <v>46317</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Date of Execution</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -1075,7 +1182,7 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>SPM-26-TC01</t>
+          <t>SPM-26-TC02</t>
         </is>
       </c>
     </row>
@@ -1087,11 +1194,11 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>The organiser who raised the request sees the open clarification on the event and on the Update request page, with the request's current details filled in</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="125.5" customHeight="1">
+          <t>The organiser changes fields the coordinator asked about and one they did not, resubmits, and the event stays Under review with the clarification answered</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="112" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -1099,13 +1206,13 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>Test data loaded: `npm run fixtures:spm26` has been run from the project folder (it only touches the 'SPM26 …' events, never anyone else's data).
-'SPM26 Meridian Advisory Briefing' is Under review, raised by Rachel Ng and assigned to Daniel Tan, with a clarification Daniel Tan opened on 20 Oct 2026, 10:00 about Description and Expected attendance.
+          <t>Run `npm run fixtures:spm26` before this case: it resubmits 'SPM26 Meridian Advisory Briefing'. Go straight on to SPM-26-TC03 and reset after that one.
+'SPM26 Meridian Advisory Briefing' is Under review, raised by Rachel Ng and assigned to Daniel Tan, with a clarification open about Description and Expected attendance.
 Logged in as Event Organiser Rachel Ng (rachel.ng@meridianfina.com / password123).</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="71.5" customHeight="1">
+    <row r="5" ht="125.5" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -1115,11 +1222,15 @@
         <is>
           <t>1. Click 'My Events' in the sidebar and open 'SPM26 Meridian Advisory Briefing'
 2. Click 'Update request' in the 'Clarification requested' banner
-3. Click 'Cancel'</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="58" customHeight="1">
+3. Replace 'Description' with the new description
+4. Replace 'Expected attendance' with 120
+5. Change 'Preferred room layout' to 'Classroom'
+6. Click 'Resubmit request'
+7. Click 'My Events' in the sidebar</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="85" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -1128,11 +1239,13 @@
       <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Event: SPM26 Meridian Advisory Briefing
-Clarification: Description, Expected attendance - 'How many advisers will attend, and is there a networking session after the briefing?'</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="247" customHeight="1">
+Description: Half-day briefing for 120 advisers, followed by a networking lunch.
+Expected attendance: 120 (was 80)
+Preferred room layout: Classroom (was Theatre - not one of the items the coordinator asked about)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="125.5" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -1140,9 +1253,8 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Step 1: The event page shows the 'Under review' badge and an amber 'Clarification requested' banner listing 'Needs clarification: Description, Expected attendance', the message 'How many advisers will attend, and is there a networking session after the briefing?', 'Asked by Daniel Tan on 20 Oct 2026, 10:00' and an 'Update request' button.
-Step 2: The 'Update request' page opens with the 'Under review' badge. At the top a 'Clarification requested' box shows the same items, message and 'Asked by Daniel Tan on 20 Oct 2026, 10:00'. The form is filled in with the request as it stands: Event name 'SPM26 Meridian Advisory Briefing', Type of event 'Conference', Description 'Half-day session followed by networking.', Expected attendance '80', Preferred room layout 'Theatre'. At the bottom are 'Resubmit request' and 'Cancel'; there is no 'Save draft' or 'Submit request' button.
-Step 3: The event page opens again, still 'Under review', with the same 'Clarification requested' banner and Expected attendance '80'.</t>
+          <t>Step 6: The event page opens with a green message 'Your updated request has been sent to Daniel Tan. It stays Under review.' The status badge reads 'Under review', no 'Clarification requested' banner is shown, and Details shows Expected attendance '120', Preferred layout 'Classroom' and Description 'Half-day briefing for 120 advisers, followed by a networking lunch.'
+Step 7: 'SPM26 Meridian Advisory Briefing' is listed with the 'Under review' badge.</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1371,7 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>SPM-26-TC02</t>
+          <t>SPM-26-TC03</t>
         </is>
       </c>
     </row>
@@ -1271,11 +1383,11 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>The organiser changes fields the coordinator asked about and one they did not, resubmits, and the event stays Under review with the clarification answered</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="112" customHeight="1">
+          <t>After the organiser resubmits, the assigned coordinator sees the updated request and can carry on with the review, including asking for clarification again</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="71.5" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -1283,13 +1395,12 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>Run `npm run fixtures:spm26` before this case: it resubmits 'SPM26 Meridian Advisory Briefing'. Go straight on to SPM-26-TC03 and reset after that one.
-'SPM26 Meridian Advisory Briefing' is Under review, raised by Rachel Ng and assigned to Daniel Tan, with a clarification open about Description and Expected attendance.
-Logged in as Event Organiser Rachel Ng (rachel.ng@meridianfina.com / password123).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="125.5" customHeight="1">
+          <t>SPM-26-TC02 has just been run ('SPM26 Meridian Advisory Briefing' was resubmitted with Expected attendance 120). Run `npm run fixtures:spm26` after this case.
+Logged in as Event Coordinator Daniel Tan (daniel.tan@connectsphere.com / password123).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44.5" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -1297,17 +1408,13 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>1. Click 'My Events' in the sidebar and open 'SPM26 Meridian Advisory Briefing'
-2. Click 'Update request' in the 'Clarification requested' banner
-3. Replace 'Description' with the new description
-4. Replace 'Expected attendance' with 120
-5. Change 'Preferred room layout' to 'Classroom'
-6. Click 'Resubmit request'
-7. Click 'My Events' in the sidebar</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="85" customHeight="1">
+          <t>1. Click 'Review Queue' in the sidebar
+2. Open 'SPM26 Meridian Advisory Briefing'
+3. Click 'Review request'</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="31" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -1315,10 +1422,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Event: SPM26 Meridian Advisory Briefing
-Description: Half-day briefing for 120 advisers, followed by a networking lunch.
-Expected attendance: 120 (was 80)
-Preferred room layout: Classroom (was Theatre - not one of the items the coordinator asked about)</t>
+          <t>Event: SPM26 Meridian Advisory Briefing (resubmitted in SPM-26-TC02)</t>
         </is>
       </c>
     </row>
@@ -1330,8 +1434,9 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Step 6: The event page opens with a green message 'Your updated request has been sent to Daniel Tan. It stays Under review.' The status badge reads 'Under review', no 'Clarification requested' banner is shown, and Details shows Expected attendance '120', Preferred layout 'Classroom' and Description 'Half-day briefing for 120 advisers, followed by a networking lunch.'
-Step 7: 'SPM26 Meridian Advisory Briefing' is listed with the 'Under review' badge.</t>
+          <t>Step 1: 'SPM26 Meridian Advisory Briefing' is still listed in the Review Queue with the 'Under review' badge.
+Step 2: The event page shows the 'Under review' badge, no 'Clarification requested' banner, and Expected attendance '120', Preferred layout 'Classroom' and the new Description.
+Step 3: The 'Review request' page shows no 'Open clarification' box. Under 'Your decision' all three options are offered: 'Approve — planning can start', 'Reject this request' and 'Ask the organiser for clarification'.</t>
         </is>
       </c>
     </row>
@@ -1448,11 +1553,11 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>SPM-26-TC03</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="44.5" customHeight="1">
+          <t>SPM-26-TC04</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="31" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Summary</t>
@@ -1460,11 +1565,11 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>After the organiser resubmits, the assigned coordinator sees the updated request and can carry on with the review, including asking for clarification again</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="71.5" customHeight="1">
+          <t>A required field cleared on the Update request page is refused and nothing is resubmitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="85" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -1472,12 +1577,13 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>SPM-26-TC02 has just been run ('SPM26 Meridian Advisory Briefing' was resubmitted with Expected attendance 120). Run `npm run fixtures:spm26` after this case.
-Logged in as Event Coordinator Daniel Tan (daniel.tan@connectsphere.com / password123).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="44.5" customHeight="1">
+          <t>Test data loaded: `npm run fixtures:spm26` has been run from the project folder.
+'SPM26 Meridian Advisory Briefing' is Under review with a clarification open about Description and Expected attendance.
+Logged in as Event Organiser Rachel Ng (rachel.ng@meridianfina.com / password123).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="112" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -1485,13 +1591,16 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>1. Click 'Review Queue' in the sidebar
-2. Open 'SPM26 Meridian Advisory Briefing'
-3. Click 'Review request'</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="31" customHeight="1">
+          <t>1. Click 'My Events' in the sidebar and open 'SPM26 Meridian Advisory Briefing'
+2. Click 'Update request' in the 'Clarification requested' banner
+3. Clear 'Event name'
+4. Clear 'Expected attendance'
+5. Click 'Resubmit request'
+6. Click 'Cancel'</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44.5" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -1499,11 +1608,13 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Event: SPM26 Meridian Advisory Briefing (resubmitted in SPM-26-TC02)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="125.5" customHeight="1">
+          <t>Event: SPM26 Meridian Advisory Briefing
+Event name: empty
+Expected attendance: empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="98.5" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -1511,9 +1622,8 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Step 1: 'SPM26 Meridian Advisory Briefing' is still listed in the Review Queue with the 'Under review' badge.
-Step 2: The event page shows the 'Under review' badge, no 'Clarification requested' banner, and Expected attendance '120', Preferred layout 'Classroom' and the new Description.
-Step 3: The 'Review request' page shows no 'Open clarification' box. Under 'Your decision' all three options are offered: 'Approve — planning can start', 'Reject this request' and 'Ask the organiser for clarification'.</t>
+          <t>Step 5: The page stays on 'Update request'. 'Give the event a name so you can find it again.' is shown under Event name and 'Enter how many people you expect.' under Expected attendance, and no success message appears.
+Step 6: The event page still shows the title 'SPM26 Meridian Advisory Briefing', Expected attendance '80', the 'Under review' badge and the 'Clarification requested' banner.</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1740,7 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>SPM-26-TC04</t>
+          <t>SPM-26-TC05</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1752,7 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>A required field cleared on the Update request page is refused and nothing is resubmitted</t>
+          <t>The smallest response is accepted: resubmitting with nothing changed answers the clarification</t>
         </is>
       </c>
     </row>
@@ -1654,13 +1764,13 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>Test data loaded: `npm run fixtures:spm26` has been run from the project folder.
+          <t>Run `npm run fixtures:spm26` before and after this case: it resubmits 'SPM26 Meridian Advisory Briefing'.
 'SPM26 Meridian Advisory Briefing' is Under review with a clarification open about Description and Expected attendance.
 Logged in as Event Organiser Rachel Ng (rachel.ng@meridianfina.com / password123).</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="112" customHeight="1">
+    <row r="5" ht="85" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -1670,14 +1780,12 @@
         <is>
           <t>1. Click 'My Events' in the sidebar and open 'SPM26 Meridian Advisory Briefing'
 2. Click 'Update request' in the 'Clarification requested' banner
-3. Clear 'Event name'
-4. Clear 'Expected attendance'
-5. Click 'Resubmit request'
-6. Click 'Cancel'</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="44.5" customHeight="1">
+3. Click 'Resubmit request' without changing anything
+4. Refresh the page</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="17.5" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -1685,9 +1793,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Event: SPM26 Meridian Advisory Briefing
-Event name: empty
-Expected attendance: empty</t>
+          <t>Event: SPM26 Meridian Advisory Briefing (no field changed)</t>
         </is>
       </c>
     </row>
@@ -1699,8 +1805,8 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Step 5: The page stays on 'Update request'. 'Give the event a name so you can find it again.' is shown under Event name and 'Enter how many people you expect.' under Expected attendance, and no success message appears.
-Step 6: The event page still shows the title 'SPM26 Meridian Advisory Briefing', Expected attendance '80', the 'Under review' badge and the 'Clarification requested' banner.</t>
+          <t>Step 3: The event page opens with the green message 'Your updated request has been sent to Daniel Tan. It stays Under review.', the 'Under review' badge, no 'Clarification requested' banner, and Expected attendance '80' and Description 'Half-day session followed by networking.' unchanged.
+Step 4: The 'Under review' badge is shown and the 'Clarification requested' banner does not come back.</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1923,7 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>SPM-26-TC05</t>
+          <t>SPM-26-TC06</t>
         </is>
       </c>
     </row>
@@ -1829,11 +1935,11 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>The smallest response is accepted: resubmitting with nothing changed answers the clarification</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="85" customHeight="1">
+          <t>Another organiser of the same client sees the clarification but cannot update or resubmit the request</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="98.5" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -1841,13 +1947,13 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>Run `npm run fixtures:spm26` before and after this case: it resubmits 'SPM26 Meridian Advisory Briefing'.
-'SPM26 Meridian Advisory Briefing' is Under review with a clarification open about Description and Expected attendance.
-Logged in as Event Organiser Rachel Ng (rachel.ng@meridianfina.com / password123).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="85" customHeight="1">
+          <t>Test data loaded: `npm run fixtures:spm26` has been run from the project folder.
+'SPM26 Meridian Advisory Briefing' was raised by Rachel Ng and has an open clarification.
+Logged in as Event Organiser James Koh (james.koh@meridianfina.com / password123), Rachel Ng's colleague at Meridian Financial Group, who did not raise it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="98.5" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -1856,13 +1962,12 @@
       <c r="B5" s="13" t="inlineStr">
         <is>
           <t>1. Click 'My Events' in the sidebar and open 'SPM26 Meridian Advisory Briefing'
-2. Click 'Update request' in the 'Clarification requested' banner
-3. Click 'Resubmit request' without changing anything
-4. Refresh the page</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="17.5" customHeight="1">
+2. Note the event's reference from the browser address bar (e.g. EVT-000123)
+3. Type /events/&lt;reference from step 2&gt;/edit after the site address in the browser address bar (e.g. http://localhost:3000/events/EVT-000123/edit) and press Enter</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44.5" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -1870,11 +1975,12 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Event: SPM26 Meridian Advisory Briefing (no field changed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="98.5" customHeight="1">
+          <t>Event: SPM26 Meridian Advisory Briefing (raised by Rachel Ng)
+User: James Koh</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="85" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -1882,8 +1988,8 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Step 3: The event page opens with the green message 'Your updated request has been sent to Daniel Tan. It stays Under review.', the 'Under review' badge, no 'Clarification requested' banner, and Expected attendance '80' and Description 'Half-day session followed by networking.' unchanged.
-Step 4: The 'Under review' badge is shown and the 'Clarification requested' banner does not come back.</t>
+          <t>Step 1: The 'Clarification requested' banner is shown with 'Needs clarification: Description, Expected attendance' and the message, but there is no 'Update request' button.
+Step 3: The 'Update request' page shows the message 'Could not open this request' - 'Only the organiser who raised this request can update it.' and no form.</t>
         </is>
       </c>
     </row>
@@ -2000,189 +2106,6 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>SPM-26-TC06</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="31" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>Summary</t>
-        </is>
-      </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>Another organiser of the same client sees the clarification but cannot update or resubmit the request</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="98.5" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>Pre-conditions</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>Test data loaded: `npm run fixtures:spm26` has been run from the project folder.
-'SPM26 Meridian Advisory Briefing' was raised by Rachel Ng and has an open clarification.
-Logged in as Event Organiser James Koh (james.koh@meridianfina.com / password123), Rachel Ng's colleague at Meridian Financial Group, who did not raise it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="98.5" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>Test Steps</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>1. Click 'My Events' in the sidebar and open 'SPM26 Meridian Advisory Briefing'
-2. Note the event's reference from the browser address bar (e.g. EVT-000123)
-3. Type /events/&lt;reference from step 2&gt;/edit after the site address in the browser address bar (e.g. http://localhost:3000/events/EVT-000123/edit) and press Enter</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="44.5" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>Test Data</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Event: SPM26 Meridian Advisory Briefing (raised by Rachel Ng)
-User: James Koh</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="85" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>Step 1: The 'Clarification requested' banner is shown with 'Needs clarification: Description, Expected attendance' and the message, but there is no 'Update request' button.
-Step 3: The 'Update request' page shows the message 'Could not open this request' - 'Only the organiser who raised this request can update it.' and no form.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="17.5" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>Sammi Chua</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>Creation Date</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="n">
-        <v>46317</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Date of Execution</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Commit</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
-  <cols>
-    <col width="24.77734375" customWidth="1" min="1" max="1"/>
-    <col width="56.77734375" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="17.5" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
           <t>SPM-26-TC07</t>
         </is>
       </c>

--- a/docs/test-cases/SPM-26_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-26_Test_Cases.xlsx
@@ -22,8 +22,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -147,7 +149,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -175,6 +177,7 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1091,6 +1094,7 @@
         <v>46317</v>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
@@ -1114,7 +1118,11 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -1122,7 +1130,11 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -1130,7 +1142,11 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Sammi Chua</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -1138,7 +1154,9 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n"/>
+      <c r="B16" s="15" t="n">
+        <v>46317</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -1146,7 +1164,11 @@
           <t>Commit</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>a306dec</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1280,6 +1302,7 @@
         <v>46317</v>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
@@ -1303,7 +1326,11 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -1311,7 +1338,11 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -1319,7 +1350,11 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Sammi Chua</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -1327,7 +1362,9 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n"/>
+      <c r="B16" s="15" t="n">
+        <v>46317</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -1335,7 +1372,11 @@
           <t>Commit</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>a306dec</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1462,6 +1503,7 @@
         <v>46317</v>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
@@ -1485,7 +1527,11 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -1493,7 +1539,11 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -1501,7 +1551,11 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Sammi Chua</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -1509,7 +1563,9 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n"/>
+      <c r="B16" s="15" t="n">
+        <v>46317</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -1517,7 +1573,11 @@
           <t>Commit</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>a306dec</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1649,6 +1709,7 @@
         <v>46317</v>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
@@ -1672,7 +1733,11 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -1680,7 +1745,11 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -1688,7 +1757,11 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Sammi Chua</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -1696,7 +1769,9 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n"/>
+      <c r="B16" s="15" t="n">
+        <v>46317</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -1704,7 +1779,11 @@
           <t>Commit</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>a306dec</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1832,6 +1911,7 @@
         <v>46317</v>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
@@ -1855,7 +1935,11 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -1863,7 +1947,11 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -1871,7 +1959,11 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Sammi Chua</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -1879,7 +1971,9 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n"/>
+      <c r="B16" s="15" t="n">
+        <v>46317</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -1887,7 +1981,11 @@
           <t>Commit</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>a306dec</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2015,6 +2113,7 @@
         <v>46317</v>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
@@ -2038,7 +2137,11 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -2046,7 +2149,11 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -2054,7 +2161,11 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Sammi Chua</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -2062,7 +2173,9 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n"/>
+      <c r="B16" s="15" t="n">
+        <v>46317</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -2070,7 +2183,11 @@
           <t>Commit</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>a306dec</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2197,6 +2314,7 @@
         <v>46317</v>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
@@ -2220,7 +2338,11 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -2228,7 +2350,11 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -2236,7 +2362,11 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Sammi Chua</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -2244,7 +2374,9 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n"/>
+      <c r="B16" s="15" t="n">
+        <v>46317</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -2252,7 +2384,11 @@
           <t>Commit</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>a306dec</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/test-cases/SPM-26_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-26_Test_Cases.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="0" activeTab="7" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
@@ -22,10 +22,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -36,6 +34,7 @@
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <b val="1"/>
       <color theme="1"/>
       <sz val="10"/>
@@ -43,21 +42,25 @@
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <color theme="1"/>
       <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <color rgb="FF1155CC"/>
       <sz val="10"/>
       <u val="single"/>
@@ -112,44 +115,69 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin"/>
-      <top style="thin"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -160,8 +188,6 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -177,7 +203,15 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -457,7 +491,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="12.5"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
@@ -471,399 +505,399 @@
   </cols>
   <sheetData>
     <row r="1" ht="31" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="17" t="inlineStr">
         <is>
           <t>SPM-26: As an Event Organiser, I want to update my event request when additional information is requested so that planning can continue with accurate requirements</t>
         </is>
       </c>
-      <c r="C1" s="8" t="n"/>
-      <c r="D1" s="8" t="n"/>
-      <c r="E1" s="8" t="n"/>
-      <c r="F1" s="8" t="n"/>
-      <c r="G1" s="8" t="n"/>
-      <c r="H1" s="8" t="n"/>
-      <c r="I1" s="9" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="C1" s="15" t="n"/>
+      <c r="D1" s="15" t="n"/>
+      <c r="E1" s="15" t="n"/>
+      <c r="F1" s="15" t="n"/>
+      <c r="G1" s="15" t="n"/>
+      <c r="H1" s="15" t="n"/>
+      <c r="I1" s="16" t="n"/>
+    </row>
+    <row r="3" ht="13" customHeight="1">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="17" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="17" t="inlineStr">
         <is>
           <t>Linked AC</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="17" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="17" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="H3" s="17" t="inlineStr">
         <is>
           <t>Superseded by</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="I3" s="17" t="inlineStr">
         <is>
           <t>Change #</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+    <row r="4" ht="37.5" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>TC01</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>SPM-26-TC01</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>The organiser who raised the request sees the open clarification on the event and on the Update request page, with the request's current details filled in</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>AC1, AC2</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="14" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H4" s="11" t="n"/>
-      <c r="I4" s="11" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="H4" s="14" t="n"/>
+      <c r="I4" s="14" t="n"/>
+    </row>
+    <row r="5" ht="37.5" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>TC02</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>SPM-26-TC02</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>The organiser changes fields the coordinator asked about and one they did not, resubmits, and the event stays Under review with the clarification answered</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>AC2, AC3, AC4</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="14" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
       </c>
-      <c r="G5" s="11" t="inlineStr">
+      <c r="G5" s="14" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H5" s="11" t="n"/>
-      <c r="I5" s="11" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="H5" s="14" t="n"/>
+      <c r="I5" s="14" t="n"/>
+    </row>
+    <row r="6" ht="37.5" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>TC03</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>SPM-26-TC03</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>After the organiser resubmits, the assigned coordinator sees the updated request and can carry on with the review, including asking for clarification again</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>AC4</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H6" s="11" t="n"/>
-      <c r="I6" s="11" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="H6" s="14" t="n"/>
+      <c r="I6" s="14" t="n"/>
+    </row>
+    <row r="7" ht="25" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>TC04</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>SPM-26-TC04</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>A required field cleared on the Update request page is refused and nothing is resubmitted</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>AC2, AC3</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="14" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
       </c>
-      <c r="G7" s="11" t="inlineStr">
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H7" s="11" t="n"/>
-      <c r="I7" s="11" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="H7" s="14" t="n"/>
+      <c r="I7" s="14" t="n"/>
+    </row>
+    <row r="8" ht="25" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>TC05</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>SPM-26-TC05</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>The smallest response is accepted: resubmitting with nothing changed answers the clarification</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>AC3, AC4</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="F8" s="14" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="G8" s="14" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H8" s="11" t="n"/>
-      <c r="I8" s="11" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="H8" s="14" t="n"/>
+      <c r="I8" s="14" t="n"/>
+    </row>
+    <row r="9" ht="25" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>TC06</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>SPM-26-TC06</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>Another organiser of the same client sees the clarification but cannot update or resubmit the request</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>AC1, AC2</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
+      <c r="F9" s="14" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
       </c>
-      <c r="G9" s="11" t="inlineStr">
+      <c r="G9" s="14" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H9" s="11" t="n"/>
-      <c r="I9" s="11" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="H9" s="14" t="n"/>
+      <c r="I9" s="14" t="n"/>
+    </row>
+    <row r="10" ht="25" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>TC07</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>SPM-26-TC07</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>A request whose clarification has already been answered cannot be updated again</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>AC2, AC4</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="F10" s="14" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="G10" s="14" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H10" s="11" t="n"/>
-      <c r="I10" s="11" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="H10" s="14" t="n"/>
+      <c r="I10" s="14" t="n"/>
+    </row>
+    <row r="13" ht="13" customHeight="1">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>Acceptance Criterion</t>
         </is>
       </c>
-      <c r="C13" s="8" t="n"/>
-      <c r="D13" s="9" t="n"/>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="C13" s="15" t="n"/>
+      <c r="D13" s="16" t="n"/>
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>Covered by</t>
         </is>
       </c>
-      <c r="F13" s="9" t="n"/>
+      <c r="F13" s="16" t="n"/>
     </row>
     <row r="14" ht="31" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>The Event Organiser can view the clarification request.</t>
         </is>
       </c>
-      <c r="C14" s="8" t="n"/>
-      <c r="D14" s="9" t="n"/>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="C14" s="15" t="n"/>
+      <c r="D14" s="16" t="n"/>
+      <c r="E14" s="14" t="inlineStr">
         <is>
           <t>SPM-26-TC01
 SPM-26-TC06</t>
         </is>
       </c>
-      <c r="F14" s="9" t="n"/>
+      <c r="F14" s="16" t="n"/>
     </row>
     <row r="15" ht="71.5" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>The Event Organiser can update any field of the event request that can be edited on a draft (see: Save Draft Event Request, SPM-24) while the clarification is open.</t>
         </is>
       </c>
-      <c r="C15" s="8" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="C15" s="15" t="n"/>
+      <c r="D15" s="16" t="n"/>
+      <c r="E15" s="14" t="inlineStr">
         <is>
           <t>SPM-26-TC01
 SPM-26-TC02
@@ -872,44 +906,44 @@
 SPM-26-TC07</t>
         </is>
       </c>
-      <c r="F15" s="9" t="n"/>
+      <c r="F15" s="16" t="n"/>
     </row>
     <row r="16" ht="44.5" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>AC3</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>The Event Organiser can resubmit the updated request.</t>
         </is>
       </c>
-      <c r="C16" s="8" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="C16" s="15" t="n"/>
+      <c r="D16" s="16" t="n"/>
+      <c r="E16" s="14" t="inlineStr">
         <is>
           <t>SPM-26-TC02
 SPM-26-TC04
 SPM-26-TC05</t>
         </is>
       </c>
-      <c r="F16" s="9" t="n"/>
+      <c r="F16" s="16" t="n"/>
     </row>
     <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>AC4</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>The event stays Under review throughout, and once the Organiser responds the clarification is marked answered so the assigned Coordinator can continue the review (see: Request Event Clarification, SPM-29).</t>
         </is>
       </c>
-      <c r="C17" s="8" t="n"/>
-      <c r="D17" s="9" t="n"/>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="C17" s="15" t="n"/>
+      <c r="D17" s="16" t="n"/>
+      <c r="E17" s="14" t="inlineStr">
         <is>
           <t>SPM-26-TC02
 SPM-26-TC03
@@ -917,15 +951,15 @@
 SPM-26-TC07</t>
         </is>
       </c>
-      <c r="F17" s="9" t="n"/>
+      <c r="F17" s="16" t="n"/>
     </row>
     <row r="19" ht="98.5" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>Code reviewed</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>src/app/api/events/[id]/route.ts
 src/lib/permissions.ts
@@ -936,13 +970,13 @@
 scripts/seed-spm26.ts</t>
         </is>
       </c>
-      <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="8" t="n"/>
-      <c r="G19" s="8" t="n"/>
-      <c r="H19" s="8" t="n"/>
-      <c r="I19" s="9" t="n"/>
+      <c r="C19" s="15" t="n"/>
+      <c r="D19" s="15" t="n"/>
+      <c r="E19" s="15" t="n"/>
+      <c r="F19" s="15" t="n"/>
+      <c r="G19" s="15" t="n"/>
+      <c r="H19" s="15" t="n"/>
+      <c r="I19" s="16" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -960,13 +994,13 @@
     <mergeCell ref="B16:D16"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId7"/>
+    <hyperlink ref="A4" location="'TC01'!A1" display="TC01"/>
+    <hyperlink ref="A5" location="'TC02'!A1" display="TC02"/>
+    <hyperlink ref="A6" location="'TC03'!A1" display="TC03"/>
+    <hyperlink ref="A7" location="'TC04'!A1" display="TC04"/>
+    <hyperlink ref="A8" location="'TC05'!A1" display="TC05"/>
+    <hyperlink ref="A9" location="'TC06'!A1" display="TC06"/>
+    <hyperlink ref="A10" location="'TC07'!A1" display="TC07"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -979,13 +1013,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col width="24.77734375" customWidth="1" min="1" max="1"/>
-    <col width="56.77734375" customWidth="1" min="2" max="2"/>
+    <col width="24.81640625" customWidth="1" min="1" max="1"/>
+    <col width="56.81640625" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="13" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Item</t>
@@ -994,36 +1028,36 @@
       <c r="B1" s="2" t="n"/>
     </row>
     <row r="2" ht="17.5" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>SPM-26-TC01</t>
         </is>
       </c>
     </row>
     <row r="3" ht="44.5" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Summary</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>The organiser who raised the request sees the open clarification on the event and on the Update request page, with the request's current details filled in</t>
         </is>
       </c>
     </row>
     <row r="4" ht="125.5" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm26` has been run from the project folder (it only touches the 'SPM26 …' events, never anyone else's data).
 'SPM26 Meridian Advisory Briefing' is Under review, raised by Rachel Ng and assigned to Daniel Tan, with a clarification Daniel Tan opened on 20 Oct 2026, 10:00 about Description and Expected attendance.
@@ -1032,12 +1066,12 @@
       </c>
     </row>
     <row r="5" ht="71.5" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>1. Click 'My Events' in the sidebar and open 'SPM26 Meridian Advisory Briefing'
 2. Click 'Update request' in the 'Clarification requested' banner
@@ -1046,12 +1080,12 @@
       </c>
     </row>
     <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Event: SPM26 Meridian Advisory Briefing
 Clarification: Description, Expected attendance - 'How many advisers will attend, and is there a networking session after the briefing?'</t>
@@ -1059,12 +1093,12 @@
       </c>
     </row>
     <row r="7" ht="247" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Step 1: The event page shows the 'Under review' badge and an amber 'Clarification requested' banner listing 'Needs clarification: Description, Expected attendance', the message 'How many advisers will attend, and is there a networking session after the briefing?', 'Asked by Daniel Tan on 20 Oct 2026, 10:00' and an 'Update request' button.
 Step 2: The 'Update request' page opens with the 'Under review' badge. At the top a 'Clarification requested' box shows the same items, message and 'Asked by Daniel Tan on 20 Oct 2026, 10:00'. The form is filled in with the request as it stands: Event name 'SPM26 Meridian Advisory Briefing', Type of event 'Conference', Description 'Half-day session followed by networking.', Expected attendance '80', Preferred room layout 'Theatre'. At the bottom are 'Resubmit request' and 'Cancel'; there is no 'Save draft' or 'Submit request' button.
@@ -1073,29 +1107,29 @@
       </c>
     </row>
     <row r="8" ht="17.5" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>Sammi Chua</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+    <row r="9" ht="12.5" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B9" s="14" t="n">
+      <c r="B9" s="12" t="n">
         <v>46317</v>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
+    <row r="10" ht="12.5" customHeight="1"/>
+    <row r="11" ht="13" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Item</t>
@@ -1104,15 +1138,21 @@
       <c r="B11" s="5" t="n"/>
       <c r="C11" s="6" t="n"/>
     </row>
-    <row r="12">
+    <row r="12" ht="212.5" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
-    </row>
-    <row r="13">
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Step 1: The event page shows the 'Under review' badge and an amber 'Clarification requested' banner listing 'Needs clarification: Description, Expected attendance', the message 'How many advisers will attend, and is there a networking session after the briefing?', 'Asked by Daniel Tan on 20 Oct 2026, 10:00' and an 'Update request' button.
+Step 2: The 'Update request' page opens with the 'Under review' badge. At the top a 'Clarification requested' box shows the same items, message and 'Asked by Daniel Tan on 20 Oct 2026, 10:00'. The form is filled in with the request as it stands: Event name 'SPM26 Meridian Advisory Briefing', Type of event 'Conference', Description 'Half-day session followed by networking.', Expected attendance '80', Preferred room layout 'Theatre'. At the bottom are 'Resubmit request' and 'Cancel'; there is no 'Save draft' or 'Submit request' button.
+Step 3: The event page opens again, still 'Under review', with the same 'Clarification requested' banner and Expected attendance '80'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="12.5" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Pass/Fail/Not Executed/Blocked</t>
@@ -1124,7 +1164,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="12.5" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Remarks</t>
@@ -1136,7 +1176,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="12.5" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Executed by</t>
@@ -1148,17 +1188,17 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="12.5" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B16" s="15" t="n">
+      <c r="B16" s="13" t="n">
         <v>46317</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="12.5" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Commit</t>
@@ -1182,13 +1222,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col width="24.77734375" customWidth="1" min="1" max="1"/>
-    <col width="56.77734375" customWidth="1" min="2" max="2"/>
+    <col width="24.81640625" customWidth="1" min="1" max="1"/>
+    <col width="56.81640625" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="13" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Item</t>
@@ -1197,36 +1237,36 @@
       <c r="B1" s="2" t="n"/>
     </row>
     <row r="2" ht="17.5" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>SPM-26-TC02</t>
         </is>
       </c>
     </row>
     <row r="3" ht="44.5" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Summary</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>The organiser changes fields the coordinator asked about and one they did not, resubmits, and the event stays Under review with the clarification answered</t>
         </is>
       </c>
     </row>
     <row r="4" ht="112" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Run `npm run fixtures:spm26` before this case: it resubmits 'SPM26 Meridian Advisory Briefing'. Go straight on to SPM-26-TC03 and reset after that one.
 'SPM26 Meridian Advisory Briefing' is Under review, raised by Rachel Ng and assigned to Daniel Tan, with a clarification open about Description and Expected attendance.
@@ -1235,12 +1275,12 @@
       </c>
     </row>
     <row r="5" ht="125.5" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>1. Click 'My Events' in the sidebar and open 'SPM26 Meridian Advisory Briefing'
 2. Click 'Update request' in the 'Clarification requested' banner
@@ -1253,12 +1293,12 @@
       </c>
     </row>
     <row r="6" ht="85" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Event: SPM26 Meridian Advisory Briefing
 Description: Half-day briefing for 120 advisers, followed by a networking lunch.
@@ -1268,12 +1308,12 @@
       </c>
     </row>
     <row r="7" ht="125.5" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Step 6: The event page opens with a green message 'Your updated request has been sent to Daniel Tan. It stays Under review.' The status badge reads 'Under review', no 'Clarification requested' banner is shown, and Details shows Expected attendance '120', Preferred layout 'Classroom' and Description 'Half-day briefing for 120 advisers, followed by a networking lunch.'
 Step 7: 'SPM26 Meridian Advisory Briefing' is listed with the 'Under review' badge.</t>
@@ -1281,29 +1321,29 @@
       </c>
     </row>
     <row r="8" ht="17.5" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>Sammi Chua</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+    <row r="9" ht="12.5" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B9" s="14" t="n">
+      <c r="B9" s="12" t="n">
         <v>46317</v>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
+    <row r="10" ht="12.5" customHeight="1"/>
+    <row r="11" ht="13" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Item</t>
@@ -1312,15 +1352,20 @@
       <c r="B11" s="5" t="n"/>
       <c r="C11" s="6" t="n"/>
     </row>
-    <row r="12">
+    <row r="12" ht="100" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
-    </row>
-    <row r="13">
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Step 6: The event page opens with a green message 'Your updated request has been sent to Daniel Tan. It stays Under review.' The status badge reads 'Under review', no 'Clarification requested' banner is shown, and Details shows Expected attendance '120', Preferred layout 'Classroom' and Description 'Half-day briefing for 120 advisers, followed by a networking lunch.'
+Step 7: 'SPM26 Meridian Advisory Briefing' is listed with the 'Under review' badge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="12.5" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Pass/Fail/Not Executed/Blocked</t>
@@ -1332,7 +1377,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="12.5" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Remarks</t>
@@ -1344,7 +1389,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="12.5" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Executed by</t>
@@ -1356,17 +1401,17 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="12.5" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B16" s="15" t="n">
+      <c r="B16" s="13" t="n">
         <v>46317</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="12.5" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Commit</t>
@@ -1390,13 +1435,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col width="24.77734375" customWidth="1" min="1" max="1"/>
-    <col width="56.77734375" customWidth="1" min="2" max="2"/>
+    <col width="24.81640625" customWidth="1" min="1" max="1"/>
+    <col width="56.81640625" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="13" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Item</t>
@@ -1405,36 +1450,36 @@
       <c r="B1" s="2" t="n"/>
     </row>
     <row r="2" ht="17.5" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>SPM-26-TC03</t>
         </is>
       </c>
     </row>
     <row r="3" ht="44.5" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Summary</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>After the organiser resubmits, the assigned coordinator sees the updated request and can carry on with the review, including asking for clarification again</t>
         </is>
       </c>
     </row>
     <row r="4" ht="71.5" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>SPM-26-TC02 has just been run ('SPM26 Meridian Advisory Briefing' was resubmitted with Expected attendance 120). Run `npm run fixtures:spm26` after this case.
 Logged in as Event Coordinator Daniel Tan (daniel.tan@connectsphere.com / password123).</t>
@@ -1442,12 +1487,12 @@
       </c>
     </row>
     <row r="5" ht="44.5" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>1. Click 'Review Queue' in the sidebar
 2. Open 'SPM26 Meridian Advisory Briefing'
@@ -1456,24 +1501,24 @@
       </c>
     </row>
     <row r="6" ht="31" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Event: SPM26 Meridian Advisory Briefing (resubmitted in SPM-26-TC02)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="125.5" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Step 1: 'SPM26 Meridian Advisory Briefing' is still listed in the Review Queue with the 'Under review' badge.
 Step 2: The event page shows the 'Under review' badge, no 'Clarification requested' banner, and Expected attendance '120', Preferred layout 'Classroom' and the new Description.
@@ -1482,29 +1527,29 @@
       </c>
     </row>
     <row r="8" ht="17.5" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>Sammi Chua</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+    <row r="9" ht="12.5" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B9" s="14" t="n">
+      <c r="B9" s="12" t="n">
         <v>46317</v>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
+    <row r="10" ht="12.5" customHeight="1"/>
+    <row r="11" ht="13" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Item</t>
@@ -1513,15 +1558,21 @@
       <c r="B11" s="5" t="n"/>
       <c r="C11" s="6" t="n"/>
     </row>
-    <row r="12">
+    <row r="12" ht="112.5" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
-    </row>
-    <row r="13">
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Step 1: 'SPM26 Meridian Advisory Briefing' is still listed in the Review Queue with the 'Under review' badge.
+Step 2: The event page shows the 'Under review' badge, no 'Clarification requested' banner, and Expected attendance '120', Preferred layout 'Classroom' and the new Description.
+Step 3: The 'Review request' page shows no 'Open clarification' box. Under 'Your decision' all three options are offered: 'Approve — planning can start', 'Reject this request' and 'Ask the organiser for clarification'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="12.5" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Pass/Fail/Not Executed/Blocked</t>
@@ -1533,7 +1584,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="12.5" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Remarks</t>
@@ -1545,7 +1596,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="12.5" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Executed by</t>
@@ -1557,17 +1608,17 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="12.5" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B16" s="15" t="n">
+      <c r="B16" s="13" t="n">
         <v>46317</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="12.5" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Commit</t>
@@ -1591,13 +1642,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col width="24.77734375" customWidth="1" min="1" max="1"/>
-    <col width="56.77734375" customWidth="1" min="2" max="2"/>
+    <col width="24.81640625" customWidth="1" min="1" max="1"/>
+    <col width="56.81640625" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="13" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Item</t>
@@ -1606,36 +1657,36 @@
       <c r="B1" s="2" t="n"/>
     </row>
     <row r="2" ht="17.5" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>SPM-26-TC04</t>
         </is>
       </c>
     </row>
     <row r="3" ht="31" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Summary</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>A required field cleared on the Update request page is refused and nothing is resubmitted</t>
         </is>
       </c>
     </row>
     <row r="4" ht="85" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm26` has been run from the project folder.
 'SPM26 Meridian Advisory Briefing' is Under review with a clarification open about Description and Expected attendance.
@@ -1644,12 +1695,12 @@
       </c>
     </row>
     <row r="5" ht="112" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>1. Click 'My Events' in the sidebar and open 'SPM26 Meridian Advisory Briefing'
 2. Click 'Update request' in the 'Clarification requested' banner
@@ -1661,12 +1712,12 @@
       </c>
     </row>
     <row r="6" ht="44.5" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Event: SPM26 Meridian Advisory Briefing
 Event name: empty
@@ -1675,12 +1726,12 @@
       </c>
     </row>
     <row r="7" ht="98.5" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Step 5: The page stays on 'Update request'. 'Give the event a name so you can find it again.' is shown under Event name and 'Enter how many people you expect.' under Expected attendance, and no success message appears.
 Step 6: The event page still shows the title 'SPM26 Meridian Advisory Briefing', Expected attendance '80', the 'Under review' badge and the 'Clarification requested' banner.</t>
@@ -1688,29 +1739,29 @@
       </c>
     </row>
     <row r="8" ht="17.5" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>Sammi Chua</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+    <row r="9" ht="12.5" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B9" s="14" t="n">
+      <c r="B9" s="12" t="n">
         <v>46317</v>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
+    <row r="10" ht="12.5" customHeight="1"/>
+    <row r="11" ht="13" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Item</t>
@@ -1719,15 +1770,20 @@
       <c r="B11" s="5" t="n"/>
       <c r="C11" s="6" t="n"/>
     </row>
-    <row r="12">
+    <row r="12" ht="87.5" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
-    </row>
-    <row r="13">
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Step 5: The page stays on 'Update request'. 'Give the event a name so you can find it again.' is shown under Event name and 'Enter how many people you expect.' under Expected attendance, and no success message appears.
+Step 6: The event page still shows the title 'SPM26 Meridian Advisory Briefing', Expected attendance '80', the 'Under review' badge and the 'Clarification requested' banner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="12.5" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Pass/Fail/Not Executed/Blocked</t>
@@ -1739,7 +1795,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="12.5" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Remarks</t>
@@ -1751,7 +1807,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="12.5" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Executed by</t>
@@ -1763,17 +1819,17 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="12.5" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B16" s="15" t="n">
+      <c r="B16" s="13" t="n">
         <v>46317</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="12.5" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Commit</t>
@@ -1797,13 +1853,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col width="24.77734375" customWidth="1" min="1" max="1"/>
-    <col width="56.77734375" customWidth="1" min="2" max="2"/>
+    <col width="24.81640625" customWidth="1" min="1" max="1"/>
+    <col width="56.81640625" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="13" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Item</t>
@@ -1812,36 +1868,36 @@
       <c r="B1" s="2" t="n"/>
     </row>
     <row r="2" ht="17.5" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>SPM-26-TC05</t>
         </is>
       </c>
     </row>
     <row r="3" ht="31" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Summary</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>The smallest response is accepted: resubmitting with nothing changed answers the clarification</t>
         </is>
       </c>
     </row>
     <row r="4" ht="85" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Run `npm run fixtures:spm26` before and after this case: it resubmits 'SPM26 Meridian Advisory Briefing'.
 'SPM26 Meridian Advisory Briefing' is Under review with a clarification open about Description and Expected attendance.
@@ -1850,12 +1906,12 @@
       </c>
     </row>
     <row r="5" ht="85" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>1. Click 'My Events' in the sidebar and open 'SPM26 Meridian Advisory Briefing'
 2. Click 'Update request' in the 'Clarification requested' banner
@@ -1865,24 +1921,24 @@
       </c>
     </row>
     <row r="6" ht="17.5" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Event: SPM26 Meridian Advisory Briefing (no field changed)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="98.5" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Step 3: The event page opens with the green message 'Your updated request has been sent to Daniel Tan. It stays Under review.', the 'Under review' badge, no 'Clarification requested' banner, and Expected attendance '80' and Description 'Half-day session followed by networking.' unchanged.
 Step 4: The 'Under review' badge is shown and the 'Clarification requested' banner does not come back.</t>
@@ -1890,29 +1946,29 @@
       </c>
     </row>
     <row r="8" ht="17.5" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>Sammi Chua</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+    <row r="9" ht="12.5" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B9" s="14" t="n">
+      <c r="B9" s="12" t="n">
         <v>46317</v>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
+    <row r="10" ht="12.5" customHeight="1"/>
+    <row r="11" ht="13" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Item</t>
@@ -1921,15 +1977,20 @@
       <c r="B11" s="5" t="n"/>
       <c r="C11" s="6" t="n"/>
     </row>
-    <row r="12">
+    <row r="12" ht="87.5" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
-    </row>
-    <row r="13">
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Step 3: The event page opens with the green message 'Your updated request has been sent to Daniel Tan. It stays Under review.', the 'Under review' badge, no 'Clarification requested' banner, and Expected attendance '80' and Description 'Half-day session followed by networking.' unchanged.
+Step 4: The 'Under review' badge is shown and the 'Clarification requested' banner does not come back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="12.5" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Pass/Fail/Not Executed/Blocked</t>
@@ -1941,7 +2002,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="12.5" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Remarks</t>
@@ -1953,7 +2014,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="12.5" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Executed by</t>
@@ -1965,17 +2026,17 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="12.5" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B16" s="15" t="n">
+      <c r="B16" s="13" t="n">
         <v>46317</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="12.5" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Commit</t>
@@ -1999,13 +2060,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col width="24.77734375" customWidth="1" min="1" max="1"/>
-    <col width="56.77734375" customWidth="1" min="2" max="2"/>
+    <col width="24.81640625" customWidth="1" min="1" max="1"/>
+    <col width="56.81640625" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="13" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Item</t>
@@ -2014,36 +2075,36 @@
       <c r="B1" s="2" t="n"/>
     </row>
     <row r="2" ht="17.5" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>SPM-26-TC06</t>
         </is>
       </c>
     </row>
     <row r="3" ht="31" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Summary</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>Another organiser of the same client sees the clarification but cannot update or resubmit the request</t>
         </is>
       </c>
     </row>
     <row r="4" ht="98.5" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm26` has been run from the project folder.
 'SPM26 Meridian Advisory Briefing' was raised by Rachel Ng and has an open clarification.
@@ -2052,12 +2113,12 @@
       </c>
     </row>
     <row r="5" ht="98.5" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>1. Click 'My Events' in the sidebar and open 'SPM26 Meridian Advisory Briefing'
 2. Note the event's reference from the browser address bar (e.g. EVT-000123)
@@ -2066,12 +2127,12 @@
       </c>
     </row>
     <row r="6" ht="44.5" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Event: SPM26 Meridian Advisory Briefing (raised by Rachel Ng)
 User: James Koh</t>
@@ -2079,12 +2140,12 @@
       </c>
     </row>
     <row r="7" ht="85" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Step 1: The 'Clarification requested' banner is shown with 'Needs clarification: Description, Expected attendance' and the message, but there is no 'Update request' button.
 Step 3: The 'Update request' page shows the message 'Could not open this request' - 'Only the organiser who raised this request can update it.' and no form.</t>
@@ -2092,29 +2153,29 @@
       </c>
     </row>
     <row r="8" ht="17.5" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>Sammi Chua</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+    <row r="9" ht="12.5" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B9" s="14" t="n">
+      <c r="B9" s="12" t="n">
         <v>46317</v>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
+    <row r="10" ht="12.5" customHeight="1"/>
+    <row r="11" ht="13" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Item</t>
@@ -2123,15 +2184,20 @@
       <c r="B11" s="5" t="n"/>
       <c r="C11" s="6" t="n"/>
     </row>
-    <row r="12">
+    <row r="12" ht="75" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
-    </row>
-    <row r="13">
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Step 1: The 'Clarification requested' banner is shown with 'Needs clarification: Description, Expected attendance' and the message, but there is no 'Update request' button.
+Step 3: The 'Update request' page shows the message 'Could not open this request' - 'Only the organiser who raised this request can update it.' and no form.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="12.5" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Pass/Fail/Not Executed/Blocked</t>
@@ -2143,7 +2209,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="12.5" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Remarks</t>
@@ -2155,7 +2221,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="12.5" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Executed by</t>
@@ -2167,17 +2233,17 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="12.5" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B16" s="15" t="n">
+      <c r="B16" s="13" t="n">
         <v>46317</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="12.5" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Commit</t>
@@ -2201,13 +2267,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col width="24.77734375" customWidth="1" min="1" max="1"/>
-    <col width="56.77734375" customWidth="1" min="2" max="2"/>
+    <col width="24.81640625" customWidth="1" min="1" max="1"/>
+    <col width="56.81640625" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="13" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Item</t>
@@ -2216,36 +2282,36 @@
       <c r="B1" s="2" t="n"/>
     </row>
     <row r="2" ht="17.5" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>SPM-26-TC07</t>
         </is>
       </c>
     </row>
     <row r="3" ht="31" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Summary</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>A request whose clarification has already been answered cannot be updated again</t>
         </is>
       </c>
     </row>
     <row r="4" ht="98.5" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm26` has been run from the project folder.
 'SPM26 Meridian Answered Workshop' is Under review, raised by Rachel Ng and assigned to Daniel Tan; its only clarification was answered on 16 Oct 2026, so none is open.
@@ -2254,12 +2320,12 @@
       </c>
     </row>
     <row r="5" ht="98.5" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>1. Click 'My Events' in the sidebar and open 'SPM26 Meridian Answered Workshop'
 2. Note the event's reference from the browser address bar (e.g. EVT-000123)
@@ -2268,24 +2334,24 @@
       </c>
     </row>
     <row r="6" ht="31" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Event: SPM26 Meridian Answered Workshop (clarification answered, none open)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="85" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Step 1: The event page shows the 'Under review' badge, no 'Clarification requested' banner and no 'Update request' button.
 Step 3: The page shows the message 'Could not open this request' - 'This request has no open clarification to answer, so it can't be changed here.' and no form.</t>
@@ -2293,29 +2359,29 @@
       </c>
     </row>
     <row r="8" ht="17.5" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>Sammi Chua</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+    <row r="9" ht="12.5" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B9" s="14" t="n">
+      <c r="B9" s="12" t="n">
         <v>46317</v>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
+    <row r="10" ht="12.5" customHeight="1"/>
+    <row r="11" ht="13" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Item</t>
@@ -2324,15 +2390,20 @@
       <c r="B11" s="5" t="n"/>
       <c r="C11" s="6" t="n"/>
     </row>
-    <row r="12">
+    <row r="12" ht="62.5" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
-    </row>
-    <row r="13">
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Step 1: The event page shows the 'Under review' badge, no 'Clarification requested' banner and no 'Update request' button.
+Step 3: The page shows the message 'Could not open this request' - 'This request has no open clarification to answer, so it can't be changed here.' and no form.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="12.5" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Pass/Fail/Not Executed/Blocked</t>
@@ -2344,7 +2415,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="12.5" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Remarks</t>
@@ -2356,7 +2427,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="12.5" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Executed by</t>
@@ -2368,17 +2439,17 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="12.5" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B16" s="15" t="n">
+      <c r="B16" s="13" t="n">
         <v>46317</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="12.5" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Commit</t>
